--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,120 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125736107</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106987</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Notåsagölens östra strand, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>495806</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6418966</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Frinnaryd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mats Thorin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mats Thorin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125736107</v>
       </c>
       <c r="B3" t="n">
-        <v>106987</v>
+        <v>106994</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125736107</v>
       </c>
       <c r="B3" t="n">
-        <v>106994</v>
+        <v>106997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125736107</v>
       </c>
       <c r="B3" t="n">
-        <v>106997</v>
+        <v>107001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125736107</v>
       </c>
       <c r="B3" t="n">
-        <v>107001</v>
+        <v>107002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125736107</v>
       </c>
       <c r="B3" t="n">
-        <v>107002</v>
+        <v>107004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125736107</v>
       </c>
       <c r="B3" t="n">
-        <v>107004</v>
+        <v>107006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125736107</v>
       </c>
       <c r="B3" t="n">
-        <v>107006</v>
+        <v>107010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125736107</v>
       </c>
       <c r="B3" t="n">
-        <v>107010</v>
+        <v>107023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16944-2023 artfynd.xlsx
+++ b/artfynd/A 16944-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125736107</v>
       </c>
       <c r="B3" t="n">
-        <v>107023</v>
+        <v>107026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
